--- a/docs/uat/UAT-Titipan-Pokok.xlsx
+++ b/docs/uat/UAT-Titipan-Pokok.xlsx
@@ -1,25 +1,38 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="true" firstSheet="0" minimized="false" showHorizontalScroll="true" showSheetTabs="true" showVerticalScroll="true" tabRatio="600" visibility="visible"/>
+    <workbookView windowHeight="16940" activeTab="2"/>
   </bookViews>
   <sheets>
-    <sheet name="Petunjuk" sheetId="1" r:id="rId4"/>
-    <sheet name="Data Uji" sheetId="2" r:id="rId5"/>
-    <sheet name="Skenario" sheetId="3" r:id="rId6"/>
+    <sheet name="Petunjuk" sheetId="1" r:id="rId1"/>
+    <sheet name="Data Uji" sheetId="2" r:id="rId2"/>
+    <sheet name="Skenario" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Skenario'!$A$1:$H$119</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Skenario!$A$1:$H$119</definedName>
   </definedNames>
-  <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="296">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="534" uniqueCount="297">
   <si>
     <t>UAT — Titipan Pokok &amp; Simpanan Pinjaman</t>
   </si>
@@ -226,6 +239,9 @@
   </si>
   <si>
     <t>Nominal ter-prefill 1.090.000.</t>
+  </si>
+  <si>
+    <t>OK</t>
   </si>
   <si>
     <t>Ubah nominal jadi 1.100.000, lalu Simpan.</t>
@@ -912,83 +928,220 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xml:space="preserve">
-  <numFmts count="0"/>
-  <fonts count="8">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="28">
     <font>
-      <b val="0"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <charset val="134"/>
     </font>
     <font>
-      <b val="1"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF111827"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
       <sz val="18"/>
       <color rgb="FF1F2937"/>
       <name val="Calibri"/>
+      <charset val="134"/>
     </font>
     <font>
-      <b val="0"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
       <sz val="10"/>
       <color rgb="FF6B7280"/>
       <name val="Calibri"/>
+      <charset val="134"/>
     </font>
     <font>
-      <b val="1"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
+      <b/>
       <sz val="13"/>
       <color rgb="FF1F2937"/>
       <name val="Calibri"/>
+      <charset val="134"/>
     </font>
     <font>
-      <b val="0"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
       <sz val="10"/>
       <color rgb="FF1F2937"/>
       <name val="Calibri"/>
+      <charset val="134"/>
     </font>
     <font>
-      <b val="1"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
       <sz val="11"/>
-      <color rgb="FF000000"/>
+      <color theme="1"/>
       <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
       <sz val="11"/>
-      <color rgb="FF111827"/>
+      <color rgb="FFFA7D00"/>
       <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="37">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -998,12 +1151,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF111827"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEF2F2"/>
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
@@ -1019,8 +1166,200 @@
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEF2F2"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -1043,63 +1382,357 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="18">
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment vertical="top" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment vertical="top" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="3" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment vertical="top" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="4" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment vertical="top" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="5" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf xfId="0" fontId="6" numFmtId="0" fillId="2" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="1" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="6" numFmtId="0" fillId="2" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0"/>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="1" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0"/>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="3" borderId="1" applyFont="0" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="4" borderId="1" applyFont="0" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="5" numFmtId="0" fillId="3" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="7" numFmtId="0" fillId="4" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="1" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="3" borderId="1" applyFont="0" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="5" borderId="1" applyFont="0" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="5" borderId="1" applyFont="0" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Link" xfId="6" builtinId="8"/>
+    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
+    <cellStyle name="Note" xfId="8" builtinId="10"/>
+    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
+    <cellStyle name="Title" xfId="10" builtinId="15"/>
+    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Input" xfId="16" builtinId="20"/>
+    <cellStyle name="Output" xfId="17" builtinId="21"/>
+    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
+    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
+    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Good" xfId="22" builtinId="26"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
+    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
+    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotTableStyle1"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -1384,187 +2017,173 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xml:space="preserve" mc:Ignorable="x14ac">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-  </sheetPr>
-  <dimension ref="A1:B31"/>
-  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="B1:B31"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="3" customWidth="true" style="0"/>
-    <col min="2" max="2" width="120" customWidth="true" style="0"/>
+    <col min="1" max="1" width="3" customWidth="1"/>
+    <col min="2" max="2" width="120" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
-      <c r="B1" s="1" t="s">
+    <row r="1" ht="26" spans="2:2">
+      <c r="B1" s="14" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
-      <c r="B2" s="2" t="s">
+    <row r="2" ht="29" spans="2:2">
+      <c r="B2" s="15" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
-      <c r="B4" s="3" t="s">
+    <row r="4" ht="20" spans="2:2">
+      <c r="B4" s="16" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
-      <c r="B5" s="4" t="s">
+    <row r="5" spans="2:2">
+      <c r="B5" s="17" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
-      <c r="B6" s="2" t="s">
+    <row r="6" spans="2:2">
+      <c r="B6" s="15" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
-      <c r="B8" s="3" t="s">
+    <row r="8" ht="20" spans="2:2">
+      <c r="B8" s="16" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
-      <c r="B9" s="4" t="s">
+    <row r="9" spans="2:2">
+      <c r="B9" s="17" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
-      <c r="B10" s="4" t="s">
+    <row r="10" spans="2:2">
+      <c r="B10" s="17" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
-      <c r="B11" s="4" t="s">
+    <row r="11" spans="2:2">
+      <c r="B11" s="17" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
-      <c r="B12" s="2" t="s">
+    <row r="12" ht="29" spans="2:2">
+      <c r="B12" s="15" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
-      <c r="B14" s="3" t="s">
+    <row r="14" ht="20" spans="2:2">
+      <c r="B14" s="16" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
-      <c r="B15" s="4" t="s">
+    <row r="15" spans="2:2">
+      <c r="B15" s="17" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
-      <c r="B16" s="4" t="s">
+    <row r="16" spans="2:2">
+      <c r="B16" s="17" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
-      <c r="B17" s="2" t="s">
+    <row r="17" spans="2:2">
+      <c r="B17" s="15" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
-      <c r="B19" s="3" t="s">
+    <row r="19" ht="20" spans="2:2">
+      <c r="B19" s="16" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="1:2">
-      <c r="B20" s="4" t="s">
+    <row r="20" spans="2:2">
+      <c r="B20" s="17" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
-      <c r="B21" s="2" t="s">
+    <row r="21" spans="2:2">
+      <c r="B21" s="15" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="23" spans="1:2">
-      <c r="B23" s="3" t="s">
+    <row r="23" ht="20" spans="2:2">
+      <c r="B23" s="16" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="24" spans="1:2">
-      <c r="B24" s="4" t="s">
+    <row r="24" ht="29" spans="2:2">
+      <c r="B24" s="17" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="26" spans="1:2">
-      <c r="B26" s="3" t="s">
+    <row r="26" ht="20" spans="2:2">
+      <c r="B26" s="16" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="27" spans="1:2">
-      <c r="B27" s="4" t="s">
+    <row r="27" spans="2:2">
+      <c r="B27" s="17" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="28" spans="1:2">
-      <c r="B28" s="4" t="s">
+    <row r="28" spans="2:2">
+      <c r="B28" s="17" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="30" spans="1:2">
-      <c r="B30" s="3" t="s">
+    <row r="30" ht="20" spans="2:2">
+      <c r="B30" s="16" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="31" spans="1:2">
-      <c r="B31" s="4" t="s">
+    <row r="31" ht="29" spans="2:2">
+      <c r="B31" s="17" t="s">
         <v>23</v>
       </c>
     </row>
   </sheetData>
-  <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
-  <headerFooter differentOddEven="false" differentFirst="false" scaleWithDoc="true" alignWithMargins="true">
-    <oddHeader/>
-    <oddFooter/>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
-  <tableParts count="0"/>
+  <pageSetup paperSize="1" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xml:space="preserve" mc:Ignorable="x14ac">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:D23"/>
-  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" width="8" customWidth="true" style="0"/>
-    <col min="2" max="2" width="26" customWidth="true" style="0"/>
-    <col min="3" max="3" width="70" customWidth="true" style="0"/>
-    <col min="4" max="4" width="20" customWidth="true" style="0"/>
+    <col min="1" max="1" width="8" customWidth="1"/>
+    <col min="2" max="2" width="26" customWidth="1"/>
+    <col min="3" max="3" width="70" customWidth="1"/>
+    <col min="4" max="4" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" s="6" t="s">
+    <row r="1" ht="17" spans="1:4">
+      <c r="A1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" ht="17" spans="1:4">
       <c r="A2" s="7" t="s">
         <v>28</v>
       </c>
@@ -1578,7 +2197,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" ht="17" spans="1:4">
       <c r="A3" s="7" t="s">
         <v>32</v>
       </c>
@@ -1592,7 +2211,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" ht="17" spans="1:4">
       <c r="A4" s="7" t="s">
         <v>36</v>
       </c>
@@ -1606,7 +2225,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" ht="17" spans="1:4">
       <c r="A5" s="7" t="s">
         <v>40</v>
       </c>
@@ -1620,7 +2239,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" ht="34" spans="1:4">
       <c r="A6" s="7" t="s">
         <v>44</v>
       </c>
@@ -1634,7 +2253,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" ht="17" spans="1:4">
       <c r="A7" s="7" t="s">
         <v>48</v>
       </c>
@@ -1649,182 +2268,171 @@
       </c>
     </row>
     <row r="16" spans="1:4">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="11" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="17" spans="1:4">
-      <c r="A17" s="8" t="s">
+      <c r="A17" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="B17" s="8" t="s">
+      <c r="B17" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="C17" s="8" t="s">
+      <c r="C17" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="D17" s="8" t="s">
+      <c r="D17" s="12" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="18" spans="1:4">
-      <c r="A18" s="9" t="s">
+      <c r="A18" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="B18" s="9">
+      <c r="B18" s="13">
         <v>2</v>
       </c>
-      <c r="C18" s="9">
-        <v>24.0</v>
-      </c>
-      <c r="D18" s="9">
-        <v>120.0</v>
+      <c r="C18" s="13">
+        <v>24</v>
+      </c>
+      <c r="D18" s="13">
+        <v>120</v>
       </c>
     </row>
     <row r="19" spans="1:4">
-      <c r="A19" s="9" t="s">
+      <c r="A19" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="B19" s="9">
+      <c r="B19" s="13">
         <v>2</v>
       </c>
-      <c r="C19" s="9">
-        <v>24.0</v>
-      </c>
-      <c r="D19" s="9">
-        <v>120.0</v>
+      <c r="C19" s="13">
+        <v>24</v>
+      </c>
+      <c r="D19" s="13">
+        <v>120</v>
       </c>
     </row>
     <row r="20" spans="1:4">
-      <c r="A20" s="9" t="s">
+      <c r="A20" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="B20" s="9">
+      <c r="B20" s="13">
         <v>2</v>
       </c>
-      <c r="C20" s="9">
-        <v>24.0</v>
-      </c>
-      <c r="D20" s="9">
-        <v>120.0</v>
+      <c r="C20" s="13">
+        <v>24</v>
+      </c>
+      <c r="D20" s="13">
+        <v>120</v>
       </c>
     </row>
     <row r="21" spans="1:4">
-      <c r="A21" s="9" t="s">
+      <c r="A21" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="B21" s="9">
+      <c r="B21" s="13">
         <v>2</v>
       </c>
-      <c r="C21" s="9">
-        <v>24.0</v>
-      </c>
-      <c r="D21" s="9">
-        <v>120.0</v>
+      <c r="C21" s="13">
+        <v>24</v>
+      </c>
+      <c r="D21" s="13">
+        <v>120</v>
       </c>
     </row>
     <row r="22" spans="1:4">
-      <c r="A22" s="9" t="s">
+      <c r="A22" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="B22" s="9" t="s">
+      <c r="B22" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="C22" s="9" t="s">
+      <c r="C22" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="D22" s="9">
-        <v>120.0</v>
+      <c r="D22" s="13">
+        <v>120</v>
       </c>
     </row>
     <row r="23" spans="1:4">
-      <c r="A23" s="9" t="s">
+      <c r="A23" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="B23" s="9">
+      <c r="B23" s="13">
         <v>4</v>
       </c>
-      <c r="C23" s="9">
-        <v>48.0</v>
-      </c>
-      <c r="D23" s="9">
-        <v>120.0</v>
+      <c r="C23" s="13">
+        <v>48</v>
+      </c>
+      <c r="D23" s="13">
+        <v>120</v>
       </c>
     </row>
   </sheetData>
-  <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
-  <headerFooter differentOddEven="false" differentFirst="false" scaleWithDoc="true" alignWithMargins="true">
-    <oddHeader/>
-    <oddFooter/>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
-  <tableParts count="0"/>
+  <pageSetup paperSize="1" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xml:space="preserve" mc:Ignorable="x14ac">
-  <sheetPr filterMode="1">
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:H119"/>
-  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="5" customWidth="true" style="0"/>
-    <col min="2" max="2" width="8" customWidth="true" style="0"/>
-    <col min="3" max="3" width="11" customWidth="true" style="0"/>
-    <col min="4" max="4" width="46" customWidth="true" style="0"/>
-    <col min="5" max="5" width="62" customWidth="true" style="0"/>
-    <col min="6" max="6" width="30" customWidth="true" style="0"/>
-    <col min="7" max="7" width="11" customWidth="true" style="0"/>
-    <col min="8" max="8" width="30" customWidth="true" style="0"/>
+    <col min="1" max="1" width="5" customWidth="1"/>
+    <col min="2" max="2" width="8" customWidth="1"/>
+    <col min="3" max="3" width="11" customWidth="1"/>
+    <col min="4" max="4" width="46" customWidth="1"/>
+    <col min="5" max="5" width="62" customWidth="1"/>
+    <col min="6" max="6" width="30" customWidth="1"/>
+    <col min="7" max="7" width="11" customWidth="1"/>
+    <col min="8" max="8" width="46.7421875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
-      <c r="A1" s="6" t="s">
+    <row r="1" ht="17" spans="1:8">
+      <c r="A1" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="H1" s="1" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="2" spans="1:8" customHeight="1" ht="24">
-      <c r="A2" s="13" t="s">
+    <row r="2" ht="24" customHeight="1" spans="1:8">
+      <c r="A2" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="B2" s="11"/>
-      <c r="C2" s="11"/>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="17"/>
-      <c r="H2" s="16"/>
-    </row>
-    <row r="3" spans="1:8">
-      <c r="A3" s="14">
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="5"/>
+      <c r="H2" s="4"/>
+    </row>
+    <row r="3" ht="34" spans="1:8">
+      <c r="A3" s="6">
         <v>1</v>
       </c>
       <c r="B3" s="7">
@@ -1839,12 +2447,14 @@
       <c r="E3" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="F3" s="16"/>
-      <c r="G3" s="17"/>
-      <c r="H3" s="16"/>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" s="14">
+      <c r="F3" s="4"/>
+      <c r="G3" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="H3" s="4"/>
+    </row>
+    <row r="4" ht="34" spans="1:8">
+      <c r="A4" s="6">
         <v>2</v>
       </c>
       <c r="B4" s="7">
@@ -1854,17 +2464,19 @@
         <v>66</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="F4" s="16"/>
-      <c r="G4" s="17"/>
-      <c r="H4" s="16"/>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" s="14">
+        <v>71</v>
+      </c>
+      <c r="F4" s="4"/>
+      <c r="G4" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="H4" s="4"/>
+    </row>
+    <row r="5" ht="34" spans="1:8">
+      <c r="A5" s="6">
         <v>3</v>
       </c>
       <c r="B5" s="7">
@@ -1874,17 +2486,19 @@
         <v>66</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="F5" s="16"/>
-      <c r="G5" s="17"/>
-      <c r="H5" s="16"/>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6" s="14">
+        <v>73</v>
+      </c>
+      <c r="F5" s="4"/>
+      <c r="G5" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="H5" s="4"/>
+    </row>
+    <row r="6" ht="34" spans="1:8">
+      <c r="A6" s="6">
         <v>4</v>
       </c>
       <c r="B6" s="7">
@@ -1894,17 +2508,19 @@
         <v>66</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="F6" s="16"/>
-      <c r="G6" s="17"/>
-      <c r="H6" s="16"/>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7" s="14">
+        <v>75</v>
+      </c>
+      <c r="F6" s="4"/>
+      <c r="G6" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="H6" s="4"/>
+    </row>
+    <row r="7" ht="34" spans="1:8">
+      <c r="A7" s="6">
         <v>5</v>
       </c>
       <c r="B7" s="7">
@@ -1914,17 +2530,19 @@
         <v>66</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="F7" s="16"/>
-      <c r="G7" s="17"/>
-      <c r="H7" s="16"/>
-    </row>
-    <row r="8" spans="1:8">
-      <c r="A8" s="14">
+        <v>77</v>
+      </c>
+      <c r="F7" s="4"/>
+      <c r="G7" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="H7" s="4"/>
+    </row>
+    <row r="8" ht="17" spans="1:8">
+      <c r="A8" s="6">
         <v>6</v>
       </c>
       <c r="B8" s="7">
@@ -1934,17 +2552,19 @@
         <v>66</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="F8" s="16"/>
-      <c r="G8" s="17"/>
-      <c r="H8" s="16"/>
-    </row>
-    <row r="9" spans="1:8">
-      <c r="A9" s="14">
+        <v>79</v>
+      </c>
+      <c r="F8" s="4"/>
+      <c r="G8" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="H8" s="4"/>
+    </row>
+    <row r="9" ht="17" spans="1:8">
+      <c r="A9" s="6">
         <v>7</v>
       </c>
       <c r="B9" s="7">
@@ -1954,17 +2574,19 @@
         <v>66</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="F9" s="16"/>
-      <c r="G9" s="17"/>
-      <c r="H9" s="16"/>
-    </row>
-    <row r="10" spans="1:8">
-      <c r="A10" s="14">
+        <v>81</v>
+      </c>
+      <c r="F9" s="4"/>
+      <c r="G9" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="H9" s="4"/>
+    </row>
+    <row r="10" ht="17" spans="1:8">
+      <c r="A10" s="6">
         <v>8</v>
       </c>
       <c r="B10" s="7">
@@ -1974,29 +2596,31 @@
         <v>66</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="F10" s="16"/>
-      <c r="G10" s="17"/>
-      <c r="H10" s="16"/>
-    </row>
-    <row r="11" spans="1:8" customHeight="1" ht="24">
-      <c r="A11" s="13" t="s">
         <v>83</v>
       </c>
-      <c r="B11" s="11"/>
-      <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="11"/>
-      <c r="F11" s="16"/>
-      <c r="G11" s="17"/>
-      <c r="H11" s="16"/>
-    </row>
-    <row r="12" spans="1:8">
-      <c r="A12" s="14">
+      <c r="F10" s="4"/>
+      <c r="G10" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="H10" s="4"/>
+    </row>
+    <row r="11" ht="24" customHeight="1" spans="1:8">
+      <c r="A11" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B11" s="3"/>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="4"/>
+      <c r="G11" s="5"/>
+      <c r="H11" s="4"/>
+    </row>
+    <row r="12" ht="17" spans="1:8">
+      <c r="A12" s="6">
         <v>9</v>
       </c>
       <c r="B12" s="7">
@@ -2006,17 +2630,19 @@
         <v>66</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="F12" s="16"/>
-      <c r="G12" s="17"/>
-      <c r="H12" s="16"/>
-    </row>
-    <row r="13" spans="1:8">
-      <c r="A13" s="14">
+        <v>86</v>
+      </c>
+      <c r="F12" s="4"/>
+      <c r="G12" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="H12" s="4"/>
+    </row>
+    <row r="13" ht="34" spans="1:8">
+      <c r="A13" s="6">
         <v>10</v>
       </c>
       <c r="B13" s="7">
@@ -2026,17 +2652,19 @@
         <v>66</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="F13" s="16"/>
-      <c r="G13" s="17"/>
-      <c r="H13" s="16"/>
-    </row>
-    <row r="14" spans="1:8">
-      <c r="A14" s="14">
+        <v>88</v>
+      </c>
+      <c r="F13" s="4"/>
+      <c r="G13" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="H13" s="4"/>
+    </row>
+    <row r="14" ht="17" spans="1:8">
+      <c r="A14" s="6">
         <v>11</v>
       </c>
       <c r="B14" s="7">
@@ -2046,17 +2674,19 @@
         <v>66</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="F14" s="16"/>
-      <c r="G14" s="17"/>
-      <c r="H14" s="16"/>
-    </row>
-    <row r="15" spans="1:8">
-      <c r="A15" s="14">
+        <v>90</v>
+      </c>
+      <c r="F14" s="4"/>
+      <c r="G14" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="H14" s="4"/>
+    </row>
+    <row r="15" ht="17" spans="1:8">
+      <c r="A15" s="6">
         <v>12</v>
       </c>
       <c r="B15" s="7">
@@ -2066,17 +2696,19 @@
         <v>66</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="F15" s="16"/>
-      <c r="G15" s="17"/>
-      <c r="H15" s="16"/>
-    </row>
-    <row r="16" spans="1:8">
-      <c r="A16" s="14">
+        <v>92</v>
+      </c>
+      <c r="F15" s="4"/>
+      <c r="G15" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="H15" s="4"/>
+    </row>
+    <row r="16" ht="17" spans="1:8">
+      <c r="A16" s="6">
         <v>13</v>
       </c>
       <c r="B16" s="7">
@@ -2086,17 +2718,19 @@
         <v>66</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="F16" s="16"/>
-      <c r="G16" s="17"/>
-      <c r="H16" s="16"/>
-    </row>
-    <row r="17" spans="1:8">
-      <c r="A17" s="14">
+        <v>94</v>
+      </c>
+      <c r="F16" s="4"/>
+      <c r="G16" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="H16" s="4"/>
+    </row>
+    <row r="17" ht="34" spans="1:8">
+      <c r="A17" s="6">
         <v>14</v>
       </c>
       <c r="B17" s="7">
@@ -2106,17 +2740,19 @@
         <v>66</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="F17" s="16"/>
-      <c r="G17" s="17"/>
-      <c r="H17" s="16"/>
-    </row>
-    <row r="18" spans="1:8">
-      <c r="A18" s="14">
+        <v>96</v>
+      </c>
+      <c r="F17" s="4"/>
+      <c r="G17" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="H17" s="4"/>
+    </row>
+    <row r="18" ht="34" spans="1:8">
+      <c r="A18" s="6">
         <v>15</v>
       </c>
       <c r="B18" s="7">
@@ -2126,17 +2762,19 @@
         <v>66</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="F18" s="16"/>
-      <c r="G18" s="17"/>
-      <c r="H18" s="16"/>
-    </row>
-    <row r="19" spans="1:8">
-      <c r="A19" s="14">
+        <v>98</v>
+      </c>
+      <c r="F18" s="4"/>
+      <c r="G18" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="H18" s="4"/>
+    </row>
+    <row r="19" ht="17" spans="1:8">
+      <c r="A19" s="6">
         <v>16</v>
       </c>
       <c r="B19" s="7">
@@ -2146,17 +2784,19 @@
         <v>66</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="F19" s="16"/>
-      <c r="G19" s="17"/>
-      <c r="H19" s="16"/>
-    </row>
-    <row r="20" spans="1:8">
-      <c r="A20" s="14">
+        <v>100</v>
+      </c>
+      <c r="F19" s="4"/>
+      <c r="G19" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="H19" s="4"/>
+    </row>
+    <row r="20" ht="34" spans="1:8">
+      <c r="A20" s="6">
         <v>17</v>
       </c>
       <c r="B20" s="7">
@@ -2166,29 +2806,31 @@
         <v>66</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="F20" s="16"/>
-      <c r="G20" s="17"/>
-      <c r="H20" s="16"/>
-    </row>
-    <row r="21" spans="1:8" customHeight="1" ht="24">
-      <c r="A21" s="13" t="s">
         <v>102</v>
       </c>
-      <c r="B21" s="11"/>
-      <c r="C21" s="11"/>
-      <c r="D21" s="11"/>
-      <c r="E21" s="11"/>
-      <c r="F21" s="16"/>
-      <c r="G21" s="17"/>
-      <c r="H21" s="16"/>
-    </row>
-    <row r="22" spans="1:8">
-      <c r="A22" s="14">
+      <c r="F20" s="4"/>
+      <c r="G20" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="H20" s="4"/>
+    </row>
+    <row r="21" ht="24" customHeight="1" spans="1:8">
+      <c r="A21" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B21" s="3"/>
+      <c r="C21" s="3"/>
+      <c r="D21" s="3"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="4"/>
+      <c r="G21" s="5"/>
+      <c r="H21" s="4"/>
+    </row>
+    <row r="22" ht="17" spans="1:8">
+      <c r="A22" s="6">
         <v>18</v>
       </c>
       <c r="B22" s="7">
@@ -2198,17 +2840,19 @@
         <v>66</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="F22" s="16"/>
-      <c r="G22" s="17"/>
-      <c r="H22" s="16"/>
-    </row>
-    <row r="23" spans="1:8">
-      <c r="A23" s="14">
+        <v>105</v>
+      </c>
+      <c r="F22" s="4"/>
+      <c r="G22" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="H22" s="4"/>
+    </row>
+    <row r="23" ht="17" spans="1:8">
+      <c r="A23" s="6">
         <v>19</v>
       </c>
       <c r="B23" s="7">
@@ -2218,17 +2862,19 @@
         <v>66</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="F23" s="16"/>
-      <c r="G23" s="17"/>
-      <c r="H23" s="16"/>
-    </row>
-    <row r="24" spans="1:8">
-      <c r="A24" s="14">
+        <v>107</v>
+      </c>
+      <c r="F23" s="4"/>
+      <c r="G23" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="H23" s="4"/>
+    </row>
+    <row r="24" ht="17" spans="1:8">
+      <c r="A24" s="6">
         <v>20</v>
       </c>
       <c r="B24" s="7">
@@ -2238,17 +2884,19 @@
         <v>66</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="F24" s="16"/>
-      <c r="G24" s="17"/>
-      <c r="H24" s="16"/>
-    </row>
-    <row r="25" spans="1:8">
-      <c r="A25" s="14">
+        <v>109</v>
+      </c>
+      <c r="F24" s="4"/>
+      <c r="G24" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="H24" s="4"/>
+    </row>
+    <row r="25" ht="17" spans="1:8">
+      <c r="A25" s="6">
         <v>21</v>
       </c>
       <c r="B25" s="7">
@@ -2258,17 +2906,19 @@
         <v>66</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E25" s="7">
-        <v>0.0</v>
-      </c>
-      <c r="F25" s="16"/>
-      <c r="G25" s="17"/>
-      <c r="H25" s="16"/>
-    </row>
-    <row r="26" spans="1:8">
-      <c r="A26" s="14">
+        <v>0</v>
+      </c>
+      <c r="F25" s="4"/>
+      <c r="G25" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="H25" s="4"/>
+    </row>
+    <row r="26" ht="17" spans="1:8">
+      <c r="A26" s="6">
         <v>22</v>
       </c>
       <c r="B26" s="7">
@@ -2278,17 +2928,19 @@
         <v>66</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="F26" s="16"/>
-      <c r="G26" s="17"/>
-      <c r="H26" s="16"/>
-    </row>
-    <row r="27" spans="1:8">
-      <c r="A27" s="14">
+        <v>112</v>
+      </c>
+      <c r="F26" s="4"/>
+      <c r="G26" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="H26" s="4"/>
+    </row>
+    <row r="27" ht="17" spans="1:8">
+      <c r="A27" s="6">
         <v>23</v>
       </c>
       <c r="B27" s="7">
@@ -2298,29 +2950,31 @@
         <v>66</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="F27" s="16"/>
-      <c r="G27" s="17"/>
-      <c r="H27" s="16"/>
-    </row>
-    <row r="28" spans="1:8" customHeight="1" ht="24">
-      <c r="A28" s="13" t="s">
         <v>114</v>
       </c>
-      <c r="B28" s="11"/>
-      <c r="C28" s="11"/>
-      <c r="D28" s="11"/>
-      <c r="E28" s="11"/>
-      <c r="F28" s="16"/>
-      <c r="G28" s="17"/>
-      <c r="H28" s="16"/>
-    </row>
-    <row r="29" spans="1:8">
-      <c r="A29" s="14">
+      <c r="F27" s="4"/>
+      <c r="G27" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="H27" s="4"/>
+    </row>
+    <row r="28" ht="24" customHeight="1" spans="1:8">
+      <c r="A28" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B28" s="3"/>
+      <c r="C28" s="3"/>
+      <c r="D28" s="3"/>
+      <c r="E28" s="3"/>
+      <c r="F28" s="4"/>
+      <c r="G28" s="5"/>
+      <c r="H28" s="4"/>
+    </row>
+    <row r="29" ht="34" spans="1:8">
+      <c r="A29" s="6">
         <v>24</v>
       </c>
       <c r="B29" s="7">
@@ -2330,17 +2984,19 @@
         <v>66</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="F29" s="16"/>
-      <c r="G29" s="17"/>
-      <c r="H29" s="16"/>
-    </row>
-    <row r="30" spans="1:8">
-      <c r="A30" s="14">
+        <v>117</v>
+      </c>
+      <c r="F29" s="4"/>
+      <c r="G29" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="H29" s="4"/>
+    </row>
+    <row r="30" ht="17" spans="1:8">
+      <c r="A30" s="6">
         <v>25</v>
       </c>
       <c r="B30" s="7">
@@ -2350,17 +3006,19 @@
         <v>66</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E30" s="7" t="s">
-        <v>118</v>
-      </c>
-      <c r="F30" s="16"/>
-      <c r="G30" s="17"/>
-      <c r="H30" s="16"/>
-    </row>
-    <row r="31" spans="1:8">
-      <c r="A31" s="14">
+        <v>119</v>
+      </c>
+      <c r="F30" s="4"/>
+      <c r="G30" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="H30" s="4"/>
+    </row>
+    <row r="31" ht="17" spans="1:8">
+      <c r="A31" s="6">
         <v>26</v>
       </c>
       <c r="B31" s="7">
@@ -2370,17 +3028,19 @@
         <v>66</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="F31" s="16"/>
-      <c r="G31" s="17"/>
-      <c r="H31" s="16"/>
-    </row>
-    <row r="32" spans="1:8">
-      <c r="A32" s="14">
+        <v>121</v>
+      </c>
+      <c r="F31" s="4"/>
+      <c r="G31" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="H31" s="4"/>
+    </row>
+    <row r="32" ht="17" spans="1:8">
+      <c r="A32" s="6">
         <v>27</v>
       </c>
       <c r="B32" s="7">
@@ -2390,69 +3050,75 @@
         <v>66</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E32" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="F32" s="16"/>
-      <c r="G32" s="17"/>
-      <c r="H32" s="16"/>
-    </row>
-    <row r="33" spans="1:8">
-      <c r="A33" s="15">
+        <v>123</v>
+      </c>
+      <c r="F32" s="4"/>
+      <c r="G32" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="H32" s="4"/>
+    </row>
+    <row r="33" ht="17" spans="1:8">
+      <c r="A33" s="8">
         <v>28</v>
       </c>
-      <c r="B33" s="12" t="s">
-        <v>123</v>
+      <c r="B33" s="9" t="s">
+        <v>124</v>
       </c>
       <c r="C33" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="D33" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="E33" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="F33" s="4"/>
+      <c r="G33" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="H33" s="4"/>
+    </row>
+    <row r="34" ht="51" spans="1:8">
+      <c r="A34" s="8">
+        <v>29</v>
+      </c>
+      <c r="B34" s="9" t="s">
         <v>124</v>
       </c>
-      <c r="D33" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="E33" s="10" t="s">
-        <v>126</v>
-      </c>
-      <c r="F33" s="16"/>
-      <c r="G33" s="17"/>
-      <c r="H33" s="16"/>
-    </row>
-    <row r="34" spans="1:8">
-      <c r="A34" s="15">
-        <v>29</v>
-      </c>
-      <c r="B34" s="12" t="s">
-        <v>123</v>
-      </c>
       <c r="C34" s="10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D34" s="10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E34" s="10" t="s">
-        <v>128</v>
-      </c>
-      <c r="F34" s="16"/>
-      <c r="G34" s="17"/>
-      <c r="H34" s="16"/>
-    </row>
-    <row r="35" spans="1:8" customHeight="1" ht="24">
-      <c r="A35" s="13" t="s">
         <v>129</v>
       </c>
-      <c r="B35" s="11"/>
-      <c r="C35" s="11"/>
-      <c r="D35" s="11"/>
-      <c r="E35" s="11"/>
-      <c r="F35" s="16"/>
-      <c r="G35" s="17"/>
-      <c r="H35" s="16"/>
-    </row>
-    <row r="36" spans="1:8">
-      <c r="A36" s="14">
+      <c r="F34" s="4"/>
+      <c r="G34" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="H34" s="4"/>
+    </row>
+    <row r="35" ht="24" customHeight="1" spans="1:8">
+      <c r="A35" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="B35" s="3"/>
+      <c r="C35" s="3"/>
+      <c r="D35" s="3"/>
+      <c r="E35" s="3"/>
+      <c r="F35" s="4"/>
+      <c r="G35" s="5"/>
+      <c r="H35" s="4"/>
+    </row>
+    <row r="36" ht="34" spans="1:8">
+      <c r="A36" s="6">
         <v>30</v>
       </c>
       <c r="B36" s="7">
@@ -2462,17 +3128,19 @@
         <v>66</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E36" s="7" t="s">
-        <v>131</v>
-      </c>
-      <c r="F36" s="16"/>
-      <c r="G36" s="17"/>
-      <c r="H36" s="16"/>
-    </row>
-    <row r="37" spans="1:8">
-      <c r="A37" s="14">
+        <v>132</v>
+      </c>
+      <c r="F36" s="4"/>
+      <c r="G36" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="H36" s="4"/>
+    </row>
+    <row r="37" ht="34" spans="1:8">
+      <c r="A37" s="6">
         <v>31</v>
       </c>
       <c r="B37" s="7">
@@ -2482,17 +3150,19 @@
         <v>66</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E37" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="F37" s="16"/>
-      <c r="G37" s="17"/>
-      <c r="H37" s="16"/>
-    </row>
-    <row r="38" spans="1:8">
-      <c r="A38" s="14">
+        <v>134</v>
+      </c>
+      <c r="F37" s="4"/>
+      <c r="G37" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="H37" s="4"/>
+    </row>
+    <row r="38" ht="17" spans="1:8">
+      <c r="A38" s="6">
         <v>32</v>
       </c>
       <c r="B38" s="7">
@@ -2502,17 +3172,19 @@
         <v>66</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E38" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="F38" s="16"/>
-      <c r="G38" s="17"/>
-      <c r="H38" s="16"/>
-    </row>
-    <row r="39" spans="1:8">
-      <c r="A39" s="14">
+        <v>136</v>
+      </c>
+      <c r="F38" s="4"/>
+      <c r="G38" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="H38" s="4"/>
+    </row>
+    <row r="39" ht="17" spans="1:8">
+      <c r="A39" s="6">
         <v>33</v>
       </c>
       <c r="B39" s="7">
@@ -2522,17 +3194,19 @@
         <v>66</v>
       </c>
       <c r="D39" s="7" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E39" s="7" t="s">
-        <v>137</v>
-      </c>
-      <c r="F39" s="16"/>
-      <c r="G39" s="17"/>
-      <c r="H39" s="16"/>
-    </row>
-    <row r="40" spans="1:8">
-      <c r="A40" s="14">
+        <v>138</v>
+      </c>
+      <c r="F39" s="4"/>
+      <c r="G39" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="H39" s="4"/>
+    </row>
+    <row r="40" ht="17" spans="1:8">
+      <c r="A40" s="6">
         <v>34</v>
       </c>
       <c r="B40" s="7">
@@ -2542,37 +3216,41 @@
         <v>66</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E40" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="F40" s="16"/>
-      <c r="G40" s="17"/>
-      <c r="H40" s="16"/>
-    </row>
-    <row r="41" spans="1:8">
-      <c r="A41" s="14">
+        <v>140</v>
+      </c>
+      <c r="F40" s="4"/>
+      <c r="G40" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="H40" s="4"/>
+    </row>
+    <row r="41" ht="17" spans="1:8">
+      <c r="A41" s="6">
         <v>35</v>
       </c>
       <c r="B41" s="7">
         <v>5.2</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D41" s="7" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E41" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="F41" s="16"/>
-      <c r="G41" s="17"/>
-      <c r="H41" s="16"/>
-    </row>
-    <row r="42" spans="1:8">
-      <c r="A42" s="14">
+        <v>142</v>
+      </c>
+      <c r="F41" s="4"/>
+      <c r="G41" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="H41" s="4"/>
+    </row>
+    <row r="42" ht="68" spans="1:8">
+      <c r="A42" s="6">
         <v>36</v>
       </c>
       <c r="B42" s="7">
@@ -2582,109 +3260,119 @@
         <v>66</v>
       </c>
       <c r="D42" s="7" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E42" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="F42" s="16"/>
-      <c r="G42" s="17"/>
-      <c r="H42" s="16"/>
-    </row>
-    <row r="43" spans="1:8">
-      <c r="A43" s="15">
+        <v>144</v>
+      </c>
+      <c r="F42" s="4"/>
+      <c r="G42" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="H42" s="4"/>
+    </row>
+    <row r="43" ht="34" spans="1:8">
+      <c r="A43" s="8">
         <v>37</v>
       </c>
-      <c r="B43" s="12" t="s">
-        <v>144</v>
+      <c r="B43" s="9" t="s">
+        <v>145</v>
       </c>
       <c r="C43" s="10" t="s">
         <v>66</v>
       </c>
       <c r="D43" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="E43" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="F43" s="4"/>
+      <c r="G43" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="H43" s="4"/>
+    </row>
+    <row r="44" ht="17" spans="1:8">
+      <c r="A44" s="8">
+        <v>38</v>
+      </c>
+      <c r="B44" s="9" t="s">
         <v>145</v>
       </c>
-      <c r="E43" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="F43" s="16"/>
-      <c r="G43" s="17"/>
-      <c r="H43" s="16"/>
-    </row>
-    <row r="44" spans="1:8">
-      <c r="A44" s="15">
-        <v>38</v>
-      </c>
-      <c r="B44" s="12" t="s">
-        <v>144</v>
-      </c>
       <c r="C44" s="10" t="s">
         <v>66</v>
       </c>
       <c r="D44" s="10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E44" s="10" t="s">
-        <v>148</v>
-      </c>
-      <c r="F44" s="16"/>
-      <c r="G44" s="17"/>
-      <c r="H44" s="16"/>
-    </row>
-    <row r="45" spans="1:8">
-      <c r="A45" s="15">
+        <v>149</v>
+      </c>
+      <c r="F44" s="4"/>
+      <c r="G44" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="H44" s="4"/>
+    </row>
+    <row r="45" ht="17" spans="1:8">
+      <c r="A45" s="8">
         <v>39</v>
       </c>
-      <c r="B45" s="12" t="s">
-        <v>144</v>
+      <c r="B45" s="9" t="s">
+        <v>145</v>
       </c>
       <c r="C45" s="10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D45" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>150</v>
-      </c>
-      <c r="F45" s="16"/>
-      <c r="G45" s="17"/>
-      <c r="H45" s="16"/>
-    </row>
-    <row r="46" spans="1:8">
-      <c r="A46" s="15">
+        <v>151</v>
+      </c>
+      <c r="F45" s="4"/>
+      <c r="G45" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="H45" s="4"/>
+    </row>
+    <row r="46" ht="34" spans="1:8">
+      <c r="A46" s="8">
         <v>40</v>
       </c>
-      <c r="B46" s="12" t="s">
-        <v>144</v>
+      <c r="B46" s="9" t="s">
+        <v>145</v>
       </c>
       <c r="C46" s="10" t="s">
         <v>66</v>
       </c>
       <c r="D46" s="10" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E46" s="10" t="s">
-        <v>152</v>
-      </c>
-      <c r="F46" s="16"/>
-      <c r="G46" s="17"/>
-      <c r="H46" s="16"/>
-    </row>
-    <row r="47" spans="1:8" customHeight="1" ht="24">
-      <c r="A47" s="13" t="s">
         <v>153</v>
       </c>
-      <c r="B47" s="11"/>
-      <c r="C47" s="11"/>
-      <c r="D47" s="11"/>
-      <c r="E47" s="11"/>
-      <c r="F47" s="16"/>
-      <c r="G47" s="17"/>
-      <c r="H47" s="16"/>
-    </row>
-    <row r="48" spans="1:8">
-      <c r="A48" s="14">
+      <c r="F46" s="4"/>
+      <c r="G46" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="H46" s="4"/>
+    </row>
+    <row r="47" ht="24" customHeight="1" spans="1:8">
+      <c r="A47" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="B47" s="3"/>
+      <c r="C47" s="3"/>
+      <c r="D47" s="3"/>
+      <c r="E47" s="3"/>
+      <c r="F47" s="4"/>
+      <c r="G47" s="5"/>
+      <c r="H47" s="4"/>
+    </row>
+    <row r="48" ht="34" spans="1:8">
+      <c r="A48" s="6">
         <v>41</v>
       </c>
       <c r="B48" s="7">
@@ -2694,37 +3382,41 @@
         <v>66</v>
       </c>
       <c r="D48" s="7" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E48" s="7" t="s">
-        <v>155</v>
-      </c>
-      <c r="F48" s="16"/>
-      <c r="G48" s="17"/>
-      <c r="H48" s="16"/>
-    </row>
-    <row r="49" spans="1:8">
-      <c r="A49" s="14">
+        <v>156</v>
+      </c>
+      <c r="F48" s="4"/>
+      <c r="G48" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="H48" s="4"/>
+    </row>
+    <row r="49" ht="17" spans="1:8">
+      <c r="A49" s="6">
         <v>42</v>
       </c>
       <c r="B49" s="7">
         <v>6</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>66</v>
+        <v>125</v>
       </c>
       <c r="D49" s="7" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E49" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="F49" s="16"/>
-      <c r="G49" s="17"/>
-      <c r="H49" s="16"/>
-    </row>
-    <row r="50" spans="1:8">
-      <c r="A50" s="14">
+        <v>158</v>
+      </c>
+      <c r="F49" s="4"/>
+      <c r="G49" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="H49" s="4"/>
+    </row>
+    <row r="50" ht="34" spans="1:8">
+      <c r="A50" s="6">
         <v>43</v>
       </c>
       <c r="B50" s="7">
@@ -2734,17 +3426,19 @@
         <v>66</v>
       </c>
       <c r="D50" s="7" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E50" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="F50" s="16"/>
-      <c r="G50" s="17"/>
-      <c r="H50" s="16"/>
-    </row>
-    <row r="51" spans="1:8">
-      <c r="A51" s="14">
+        <v>160</v>
+      </c>
+      <c r="F50" s="4"/>
+      <c r="G50" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="H50" s="4"/>
+    </row>
+    <row r="51" ht="17" spans="1:8">
+      <c r="A51" s="6">
         <v>44</v>
       </c>
       <c r="B51" s="7">
@@ -2754,17 +3448,19 @@
         <v>66</v>
       </c>
       <c r="D51" s="7" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E51" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="F51" s="16"/>
-      <c r="G51" s="17"/>
-      <c r="H51" s="16"/>
-    </row>
-    <row r="52" spans="1:8">
-      <c r="A52" s="14">
+        <v>162</v>
+      </c>
+      <c r="F51" s="4"/>
+      <c r="G51" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="H51" s="4"/>
+    </row>
+    <row r="52" ht="34" spans="1:8">
+      <c r="A52" s="6">
         <v>45</v>
       </c>
       <c r="B52" s="7">
@@ -2774,37 +3470,41 @@
         <v>66</v>
       </c>
       <c r="D52" s="7" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E52" s="7" t="s">
-        <v>163</v>
-      </c>
-      <c r="F52" s="16"/>
-      <c r="G52" s="17"/>
-      <c r="H52" s="16"/>
-    </row>
-    <row r="53" spans="1:8">
-      <c r="A53" s="14">
+        <v>164</v>
+      </c>
+      <c r="F52" s="4"/>
+      <c r="G52" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="H52" s="4"/>
+    </row>
+    <row r="53" ht="34" spans="1:8">
+      <c r="A53" s="6">
         <v>46</v>
       </c>
       <c r="B53" s="7">
         <v>6.1</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D53" s="7" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E53" s="7" t="s">
-        <v>165</v>
-      </c>
-      <c r="F53" s="16"/>
-      <c r="G53" s="17"/>
-      <c r="H53" s="16"/>
-    </row>
-    <row r="54" spans="1:8">
-      <c r="A54" s="14">
+        <v>166</v>
+      </c>
+      <c r="F53" s="4"/>
+      <c r="G53" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="H53" s="4"/>
+    </row>
+    <row r="54" ht="17" spans="1:8">
+      <c r="A54" s="6">
         <v>47</v>
       </c>
       <c r="B54" s="7">
@@ -2814,169 +3514,185 @@
         <v>66</v>
       </c>
       <c r="D54" s="7" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E54" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="F54" s="16"/>
-      <c r="G54" s="17"/>
-      <c r="H54" s="16"/>
-    </row>
-    <row r="55" spans="1:8">
-      <c r="A55" s="14">
+        <v>168</v>
+      </c>
+      <c r="F54" s="4"/>
+      <c r="G54" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="H54" s="4"/>
+    </row>
+    <row r="55" ht="17" spans="1:8">
+      <c r="A55" s="6">
         <v>48</v>
       </c>
       <c r="B55" s="7">
         <v>6.2</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D55" s="7" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E55" s="7" t="s">
-        <v>169</v>
-      </c>
-      <c r="F55" s="16"/>
-      <c r="G55" s="17"/>
-      <c r="H55" s="16"/>
-    </row>
-    <row r="56" spans="1:8" customHeight="1" ht="24">
-      <c r="A56" s="13" t="s">
         <v>170</v>
       </c>
-      <c r="B56" s="11"/>
-      <c r="C56" s="11"/>
-      <c r="D56" s="11"/>
-      <c r="E56" s="11"/>
-      <c r="F56" s="16"/>
-      <c r="G56" s="17"/>
-      <c r="H56" s="16"/>
-    </row>
-    <row r="57" spans="1:8">
-      <c r="A57" s="14">
+      <c r="F55" s="4"/>
+      <c r="G55" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="H55" s="4"/>
+    </row>
+    <row r="56" ht="24" customHeight="1" spans="1:8">
+      <c r="A56" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="B56" s="3"/>
+      <c r="C56" s="3"/>
+      <c r="D56" s="3"/>
+      <c r="E56" s="3"/>
+      <c r="F56" s="4"/>
+      <c r="G56" s="5"/>
+      <c r="H56" s="4"/>
+    </row>
+    <row r="57" ht="34" spans="1:8">
+      <c r="A57" s="6">
         <v>49</v>
       </c>
       <c r="B57" s="7">
         <v>7.1</v>
       </c>
       <c r="C57" s="7" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D57" s="7" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E57" s="7" t="s">
-        <v>172</v>
-      </c>
-      <c r="F57" s="16"/>
-      <c r="G57" s="17"/>
-      <c r="H57" s="16"/>
-    </row>
-    <row r="58" spans="1:8">
-      <c r="A58" s="14">
+        <v>173</v>
+      </c>
+      <c r="F57" s="4"/>
+      <c r="G57" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="H57" s="4"/>
+    </row>
+    <row r="58" ht="17" spans="1:8">
+      <c r="A58" s="6">
         <v>50</v>
       </c>
       <c r="B58" s="7">
         <v>7.1</v>
       </c>
       <c r="C58" s="7" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D58" s="7" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E58" s="7" t="s">
-        <v>174</v>
-      </c>
-      <c r="F58" s="16"/>
-      <c r="G58" s="17"/>
-      <c r="H58" s="16"/>
-    </row>
-    <row r="59" spans="1:8">
-      <c r="A59" s="14">
+        <v>175</v>
+      </c>
+      <c r="F58" s="4"/>
+      <c r="G58" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="H58" s="4"/>
+    </row>
+    <row r="59" ht="17" spans="1:8">
+      <c r="A59" s="6">
         <v>51</v>
       </c>
       <c r="B59" s="7">
         <v>7.1</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D59" s="7" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E59" s="7" t="s">
-        <v>176</v>
-      </c>
-      <c r="F59" s="16"/>
-      <c r="G59" s="17"/>
-      <c r="H59" s="16"/>
-    </row>
-    <row r="60" spans="1:8">
-      <c r="A60" s="14">
+        <v>177</v>
+      </c>
+      <c r="F59" s="4"/>
+      <c r="G59" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="H59" s="4"/>
+    </row>
+    <row r="60" ht="17" spans="1:8">
+      <c r="A60" s="6">
         <v>52</v>
       </c>
       <c r="B60" s="7">
         <v>7.1</v>
       </c>
       <c r="C60" s="7" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D60" s="7" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E60" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="F60" s="16"/>
-      <c r="G60" s="17"/>
-      <c r="H60" s="16"/>
-    </row>
-    <row r="61" spans="1:8">
-      <c r="A61" s="14">
+        <v>179</v>
+      </c>
+      <c r="F60" s="4"/>
+      <c r="G60" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="H60" s="4"/>
+    </row>
+    <row r="61" ht="17" spans="1:8">
+      <c r="A61" s="6">
         <v>53</v>
       </c>
       <c r="B61" s="7">
         <v>7.1</v>
       </c>
       <c r="C61" s="7" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D61" s="7" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E61" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="F61" s="16"/>
-      <c r="G61" s="17"/>
-      <c r="H61" s="16"/>
-    </row>
-    <row r="62" spans="1:8">
-      <c r="A62" s="14">
+        <v>181</v>
+      </c>
+      <c r="F61" s="4"/>
+      <c r="G61" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="H61" s="4"/>
+    </row>
+    <row r="62" ht="17" spans="1:8">
+      <c r="A62" s="6">
         <v>54</v>
       </c>
       <c r="B62" s="7">
         <v>7.1</v>
       </c>
       <c r="C62" s="7" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D62" s="7" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E62" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="F62" s="16"/>
-      <c r="G62" s="17"/>
-      <c r="H62" s="16"/>
-    </row>
-    <row r="63" spans="1:8">
-      <c r="A63" s="14">
+        <v>183</v>
+      </c>
+      <c r="F62" s="4"/>
+      <c r="G62" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="H62" s="4"/>
+    </row>
+    <row r="63" ht="17" spans="1:8">
+      <c r="A63" s="6">
         <v>55</v>
       </c>
       <c r="B63" s="7">
@@ -2986,17 +3702,19 @@
         <v>66</v>
       </c>
       <c r="D63" s="7" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E63" s="7" t="s">
-        <v>184</v>
-      </c>
-      <c r="F63" s="16"/>
-      <c r="G63" s="17"/>
-      <c r="H63" s="16"/>
-    </row>
-    <row r="64" spans="1:8">
-      <c r="A64" s="14">
+        <v>185</v>
+      </c>
+      <c r="F63" s="4"/>
+      <c r="G63" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="H63" s="4"/>
+    </row>
+    <row r="64" ht="17" spans="1:8">
+      <c r="A64" s="6">
         <v>56</v>
       </c>
       <c r="B64" s="7">
@@ -3006,69 +3724,75 @@
         <v>66</v>
       </c>
       <c r="D64" s="7" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E64" s="7">
-        <v>403.0</v>
-      </c>
-      <c r="F64" s="16"/>
-      <c r="G64" s="17"/>
-      <c r="H64" s="16"/>
-    </row>
-    <row r="65" spans="1:8">
-      <c r="A65" s="14">
+        <v>403</v>
+      </c>
+      <c r="F64" s="4"/>
+      <c r="G64" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="H64" s="4"/>
+    </row>
+    <row r="65" ht="17" spans="1:8">
+      <c r="A65" s="6">
         <v>57</v>
       </c>
       <c r="B65" s="7">
         <v>7.2</v>
       </c>
       <c r="C65" s="7" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D65" s="7" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E65" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="F65" s="16"/>
-      <c r="G65" s="17"/>
-      <c r="H65" s="16"/>
-    </row>
-    <row r="66" spans="1:8">
-      <c r="A66" s="14">
+        <v>187</v>
+      </c>
+      <c r="F65" s="4"/>
+      <c r="G65" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="H65" s="4"/>
+    </row>
+    <row r="66" ht="17" spans="1:8">
+      <c r="A66" s="6">
         <v>58</v>
       </c>
       <c r="B66" s="7">
         <v>7.2</v>
       </c>
       <c r="C66" s="7" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D66" s="7" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E66" s="7" t="s">
-        <v>188</v>
-      </c>
-      <c r="F66" s="16"/>
-      <c r="G66" s="17"/>
-      <c r="H66" s="16"/>
-    </row>
-    <row r="67" spans="1:8" customHeight="1" ht="24">
-      <c r="A67" s="13" t="s">
         <v>189</v>
       </c>
-      <c r="B67" s="11"/>
-      <c r="C67" s="11"/>
-      <c r="D67" s="11"/>
-      <c r="E67" s="11"/>
-      <c r="F67" s="16"/>
-      <c r="G67" s="17"/>
-      <c r="H67" s="16"/>
-    </row>
-    <row r="68" spans="1:8">
-      <c r="A68" s="14">
+      <c r="F66" s="4"/>
+      <c r="G66" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="H66" s="4"/>
+    </row>
+    <row r="67" ht="24" customHeight="1" spans="1:8">
+      <c r="A67" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="B67" s="3"/>
+      <c r="C67" s="3"/>
+      <c r="D67" s="3"/>
+      <c r="E67" s="3"/>
+      <c r="F67" s="4"/>
+      <c r="G67" s="5"/>
+      <c r="H67" s="4"/>
+    </row>
+    <row r="68" ht="34" spans="1:8">
+      <c r="A68" s="6">
         <v>59</v>
       </c>
       <c r="B68" s="7">
@@ -3078,37 +3802,41 @@
         <v>66</v>
       </c>
       <c r="D68" s="7" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E68" s="7" t="s">
-        <v>191</v>
-      </c>
-      <c r="F68" s="16"/>
-      <c r="G68" s="17"/>
-      <c r="H68" s="16"/>
-    </row>
-    <row r="69" spans="1:8">
-      <c r="A69" s="14">
+        <v>192</v>
+      </c>
+      <c r="F68" s="4"/>
+      <c r="G68" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="H68" s="4"/>
+    </row>
+    <row r="69" ht="17" spans="1:8">
+      <c r="A69" s="6">
         <v>60</v>
       </c>
       <c r="B69" s="7">
         <v>8</v>
       </c>
       <c r="C69" s="7" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D69" s="7" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E69" s="7" t="s">
-        <v>193</v>
-      </c>
-      <c r="F69" s="16"/>
-      <c r="G69" s="17"/>
-      <c r="H69" s="16"/>
-    </row>
-    <row r="70" spans="1:8">
-      <c r="A70" s="14">
+        <v>194</v>
+      </c>
+      <c r="F69" s="4"/>
+      <c r="G69" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="H69" s="4"/>
+    </row>
+    <row r="70" ht="34" spans="1:8">
+      <c r="A70" s="6">
         <v>61</v>
       </c>
       <c r="B70" s="7">
@@ -3118,529 +3846,581 @@
         <v>66</v>
       </c>
       <c r="D70" s="7" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E70" s="7" t="s">
-        <v>195</v>
-      </c>
-      <c r="F70" s="16"/>
-      <c r="G70" s="17"/>
-      <c r="H70" s="16"/>
-    </row>
-    <row r="71" spans="1:8">
-      <c r="A71" s="14">
+        <v>196</v>
+      </c>
+      <c r="F70" s="4"/>
+      <c r="G70" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="H70" s="4"/>
+    </row>
+    <row r="71" ht="34" spans="1:8">
+      <c r="A71" s="6">
         <v>62</v>
       </c>
       <c r="B71" s="7">
         <v>8</v>
       </c>
       <c r="C71" s="7" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D71" s="7" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E71" s="7" t="s">
-        <v>197</v>
-      </c>
-      <c r="F71" s="16"/>
-      <c r="G71" s="17"/>
-      <c r="H71" s="16"/>
-    </row>
-    <row r="72" spans="1:8">
-      <c r="A72" s="14">
+        <v>198</v>
+      </c>
+      <c r="F71" s="4"/>
+      <c r="G71" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="H71" s="4"/>
+    </row>
+    <row r="72" ht="34" spans="1:8">
+      <c r="A72" s="6">
         <v>63</v>
       </c>
       <c r="B72" s="7">
         <v>8</v>
       </c>
       <c r="C72" s="7" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D72" s="7" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E72" s="7" t="s">
-        <v>199</v>
-      </c>
-      <c r="F72" s="16"/>
-      <c r="G72" s="17"/>
-      <c r="H72" s="16"/>
-    </row>
-    <row r="73" spans="1:8" customHeight="1" ht="24">
-      <c r="A73" s="13" t="s">
         <v>200</v>
       </c>
-      <c r="B73" s="11"/>
-      <c r="C73" s="11"/>
-      <c r="D73" s="11"/>
-      <c r="E73" s="11"/>
-      <c r="F73" s="16"/>
-      <c r="G73" s="17"/>
-      <c r="H73" s="16"/>
-    </row>
-    <row r="74" spans="1:8">
-      <c r="A74" s="14">
+      <c r="F72" s="4"/>
+      <c r="G72" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="H72" s="4"/>
+    </row>
+    <row r="73" ht="24" customHeight="1" spans="1:8">
+      <c r="A73" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="B73" s="3"/>
+      <c r="C73" s="3"/>
+      <c r="D73" s="3"/>
+      <c r="E73" s="3"/>
+      <c r="F73" s="4"/>
+      <c r="G73" s="5"/>
+      <c r="H73" s="4"/>
+    </row>
+    <row r="74" ht="34" spans="1:8">
+      <c r="A74" s="6">
         <v>64</v>
       </c>
       <c r="B74" s="7">
         <v>9.1</v>
       </c>
       <c r="C74" s="7" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D74" s="7" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E74" s="7" t="s">
-        <v>202</v>
-      </c>
-      <c r="F74" s="16"/>
-      <c r="G74" s="17"/>
-      <c r="H74" s="16"/>
-    </row>
-    <row r="75" spans="1:8">
-      <c r="A75" s="14">
+        <v>203</v>
+      </c>
+      <c r="F74" s="4"/>
+      <c r="G74" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="H74" s="4"/>
+    </row>
+    <row r="75" ht="17" spans="1:8">
+      <c r="A75" s="6">
         <v>65</v>
       </c>
       <c r="B75" s="7">
         <v>9.1</v>
       </c>
       <c r="C75" s="7" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D75" s="7" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E75" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="F75" s="16"/>
-      <c r="G75" s="17"/>
-      <c r="H75" s="16"/>
-    </row>
-    <row r="76" spans="1:8">
-      <c r="A76" s="14">
+        <v>205</v>
+      </c>
+      <c r="F75" s="4"/>
+      <c r="G75" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="H75" s="4"/>
+    </row>
+    <row r="76" ht="34" spans="1:8">
+      <c r="A76" s="6">
         <v>66</v>
       </c>
       <c r="B76" s="7">
         <v>9.1</v>
       </c>
       <c r="C76" s="7" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D76" s="7" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E76" s="7" t="s">
-        <v>206</v>
-      </c>
-      <c r="F76" s="16"/>
-      <c r="G76" s="17"/>
-      <c r="H76" s="16"/>
-    </row>
-    <row r="77" spans="1:8">
-      <c r="A77" s="14">
+        <v>207</v>
+      </c>
+      <c r="F76" s="4"/>
+      <c r="G76" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="H76" s="4"/>
+    </row>
+    <row r="77" ht="34" spans="1:8">
+      <c r="A77" s="6">
         <v>67</v>
       </c>
       <c r="B77" s="7">
         <v>9.1</v>
       </c>
       <c r="C77" s="7" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D77" s="7" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E77" s="7" t="s">
-        <v>208</v>
-      </c>
-      <c r="F77" s="16"/>
-      <c r="G77" s="17"/>
-      <c r="H77" s="16"/>
-    </row>
-    <row r="78" spans="1:8">
-      <c r="A78" s="14">
+        <v>209</v>
+      </c>
+      <c r="F77" s="4"/>
+      <c r="G77" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="H77" s="4"/>
+    </row>
+    <row r="78" ht="34" spans="1:8">
+      <c r="A78" s="6">
         <v>68</v>
       </c>
       <c r="B78" s="7">
         <v>9.1</v>
       </c>
       <c r="C78" s="7" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D78" s="7" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E78" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="F78" s="16"/>
-      <c r="G78" s="17"/>
-      <c r="H78" s="16"/>
-    </row>
-    <row r="79" spans="1:8">
-      <c r="A79" s="14">
+        <v>211</v>
+      </c>
+      <c r="F78" s="4"/>
+      <c r="G78" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="H78" s="4"/>
+    </row>
+    <row r="79" ht="34" spans="1:8">
+      <c r="A79" s="6">
         <v>69</v>
       </c>
       <c r="B79" s="7">
         <v>9.2</v>
       </c>
       <c r="C79" s="7" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D79" s="7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E79" s="7" t="s">
-        <v>212</v>
-      </c>
-      <c r="F79" s="16"/>
-      <c r="G79" s="17"/>
-      <c r="H79" s="16"/>
-    </row>
-    <row r="80" spans="1:8">
-      <c r="A80" s="14">
+        <v>213</v>
+      </c>
+      <c r="F79" s="4"/>
+      <c r="G79" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="H79" s="4"/>
+    </row>
+    <row r="80" ht="17" spans="1:8">
+      <c r="A80" s="6">
         <v>70</v>
       </c>
       <c r="B80" s="7">
         <v>9.2</v>
       </c>
       <c r="C80" s="7" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D80" s="7" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E80" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="F80" s="16"/>
-      <c r="G80" s="17"/>
-      <c r="H80" s="16"/>
-    </row>
-    <row r="81" spans="1:8">
-      <c r="A81" s="14">
+        <v>215</v>
+      </c>
+      <c r="F80" s="4"/>
+      <c r="G80" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="H80" s="4"/>
+    </row>
+    <row r="81" ht="34" spans="1:8">
+      <c r="A81" s="6">
         <v>71</v>
       </c>
       <c r="B81" s="7">
         <v>9.3</v>
       </c>
       <c r="C81" s="7" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D81" s="7" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E81" s="7" t="s">
-        <v>216</v>
-      </c>
-      <c r="F81" s="16"/>
-      <c r="G81" s="17"/>
-      <c r="H81" s="16"/>
-    </row>
-    <row r="82" spans="1:8">
-      <c r="A82" s="14">
+        <v>217</v>
+      </c>
+      <c r="F81" s="4"/>
+      <c r="G81" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="H81" s="4"/>
+    </row>
+    <row r="82" ht="51" spans="1:8">
+      <c r="A82" s="6">
         <v>72</v>
       </c>
       <c r="B82" s="7">
         <v>9.3</v>
       </c>
       <c r="C82" s="7" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D82" s="7" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E82" s="7" t="s">
-        <v>218</v>
-      </c>
-      <c r="F82" s="16"/>
-      <c r="G82" s="17"/>
-      <c r="H82" s="16"/>
-    </row>
-    <row r="83" spans="1:8">
-      <c r="A83" s="14">
+        <v>219</v>
+      </c>
+      <c r="F82" s="4"/>
+      <c r="G82" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="H82" s="4"/>
+    </row>
+    <row r="83" ht="51" spans="1:8">
+      <c r="A83" s="6">
         <v>73</v>
       </c>
       <c r="B83" s="7" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C83" s="7" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D83" s="7" t="s">
+        <v>221</v>
+      </c>
+      <c r="E83" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="F83" s="4"/>
+      <c r="G83" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="H83" s="4"/>
+    </row>
+    <row r="84" ht="34" spans="1:8">
+      <c r="A84" s="6">
+        <v>74</v>
+      </c>
+      <c r="B84" s="7" t="s">
         <v>220</v>
       </c>
-      <c r="E83" s="7" t="s">
-        <v>221</v>
-      </c>
-      <c r="F83" s="16"/>
-      <c r="G83" s="17"/>
-      <c r="H83" s="16"/>
-    </row>
-    <row r="84" spans="1:8">
-      <c r="A84" s="14">
-        <v>74</v>
-      </c>
-      <c r="B84" s="7" t="s">
-        <v>219</v>
-      </c>
       <c r="C84" s="7" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D84" s="7" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E84" s="7" t="s">
-        <v>223</v>
-      </c>
-      <c r="F84" s="16"/>
-      <c r="G84" s="17"/>
-      <c r="H84" s="16"/>
-    </row>
-    <row r="85" spans="1:8">
-      <c r="A85" s="14">
+        <v>224</v>
+      </c>
+      <c r="F84" s="4"/>
+      <c r="G84" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="H84" s="4"/>
+    </row>
+    <row r="85" ht="17" spans="1:8">
+      <c r="A85" s="6">
         <v>75</v>
       </c>
       <c r="B85" s="7" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C85" s="7" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D85" s="7" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E85" s="7" t="s">
-        <v>225</v>
-      </c>
-      <c r="F85" s="16"/>
-      <c r="G85" s="17"/>
-      <c r="H85" s="16"/>
-    </row>
-    <row r="86" spans="1:8">
-      <c r="A86" s="15">
+        <v>226</v>
+      </c>
+      <c r="F85" s="4"/>
+      <c r="G85" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="H85" s="4"/>
+    </row>
+    <row r="86" ht="34" spans="1:8">
+      <c r="A86" s="8">
         <v>76</v>
       </c>
-      <c r="B86" s="12" t="s">
-        <v>226</v>
+      <c r="B86" s="9" t="s">
+        <v>227</v>
       </c>
       <c r="C86" s="10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D86" s="10" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E86" s="10" t="s">
-        <v>228</v>
-      </c>
-      <c r="F86" s="16"/>
-      <c r="G86" s="17"/>
-      <c r="H86" s="16"/>
-    </row>
-    <row r="87" spans="1:8">
-      <c r="A87" s="14">
+        <v>229</v>
+      </c>
+      <c r="F86" s="4"/>
+      <c r="G86" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="H86" s="4"/>
+    </row>
+    <row r="87" ht="17" spans="1:8">
+      <c r="A87" s="6">
         <v>77</v>
       </c>
       <c r="B87" s="7" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C87" s="7" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D87" s="7" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E87" s="7" t="s">
-        <v>230</v>
-      </c>
-      <c r="F87" s="16"/>
-      <c r="G87" s="17"/>
-      <c r="H87" s="16"/>
-    </row>
-    <row r="88" spans="1:8">
-      <c r="A88" s="14">
+        <v>231</v>
+      </c>
+      <c r="F87" s="4"/>
+      <c r="G87" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="H87" s="4"/>
+    </row>
+    <row r="88" ht="17" spans="1:8">
+      <c r="A88" s="6">
         <v>78</v>
       </c>
       <c r="B88" s="7" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C88" s="7" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D88" s="7" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E88" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="F88" s="16"/>
-      <c r="G88" s="17"/>
-      <c r="H88" s="16"/>
-    </row>
-    <row r="89" spans="1:8">
-      <c r="A89" s="14">
+        <v>233</v>
+      </c>
+      <c r="F88" s="4"/>
+      <c r="G88" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="H88" s="4"/>
+    </row>
+    <row r="89" ht="34" spans="1:8">
+      <c r="A89" s="6">
         <v>79</v>
       </c>
       <c r="B89" s="7" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C89" s="7" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D89" s="7" t="s">
+        <v>235</v>
+      </c>
+      <c r="E89" s="7" t="s">
+        <v>236</v>
+      </c>
+      <c r="F89" s="4"/>
+      <c r="G89" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="H89" s="4"/>
+    </row>
+    <row r="90" ht="34" spans="1:8">
+      <c r="A90" s="6">
+        <v>80</v>
+      </c>
+      <c r="B90" s="7" t="s">
         <v>234</v>
       </c>
-      <c r="E89" s="7" t="s">
-        <v>235</v>
-      </c>
-      <c r="F89" s="16"/>
-      <c r="G89" s="17"/>
-      <c r="H89" s="16"/>
-    </row>
-    <row r="90" spans="1:8">
-      <c r="A90" s="14">
-        <v>80</v>
-      </c>
-      <c r="B90" s="7" t="s">
-        <v>233</v>
-      </c>
       <c r="C90" s="7" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D90" s="7" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E90" s="7" t="s">
-        <v>237</v>
-      </c>
-      <c r="F90" s="16"/>
-      <c r="G90" s="17"/>
-      <c r="H90" s="16"/>
-    </row>
-    <row r="91" spans="1:8">
-      <c r="A91" s="14">
+        <v>238</v>
+      </c>
+      <c r="F90" s="4"/>
+      <c r="G90" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="H90" s="4"/>
+    </row>
+    <row r="91" ht="34" spans="1:8">
+      <c r="A91" s="6">
         <v>81</v>
       </c>
       <c r="B91" s="7" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C91" s="7" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D91" s="7" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E91" s="7" t="s">
-        <v>239</v>
-      </c>
-      <c r="F91" s="16"/>
-      <c r="G91" s="17"/>
-      <c r="H91" s="16"/>
-    </row>
-    <row r="92" spans="1:8">
-      <c r="A92" s="15">
+        <v>240</v>
+      </c>
+      <c r="F91" s="4"/>
+      <c r="G91" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="H91" s="4"/>
+    </row>
+    <row r="92" ht="34" spans="1:8">
+      <c r="A92" s="8">
         <v>82</v>
       </c>
-      <c r="B92" s="12" t="s">
-        <v>240</v>
+      <c r="B92" s="9" t="s">
+        <v>241</v>
       </c>
       <c r="C92" s="10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D92" s="10" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E92" s="10" t="s">
-        <v>242</v>
-      </c>
-      <c r="F92" s="16"/>
-      <c r="G92" s="17"/>
-      <c r="H92" s="16"/>
-    </row>
-    <row r="93" spans="1:8">
-      <c r="A93" s="14">
+        <v>243</v>
+      </c>
+      <c r="F92" s="4"/>
+      <c r="G92" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="H92" s="4"/>
+    </row>
+    <row r="93" ht="34" spans="1:8">
+      <c r="A93" s="6">
         <v>83</v>
       </c>
       <c r="B93" s="7" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C93" s="7" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D93" s="7" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E93" s="7" t="s">
-        <v>245</v>
-      </c>
-      <c r="F93" s="16"/>
-      <c r="G93" s="17"/>
-      <c r="H93" s="16"/>
-    </row>
-    <row r="94" spans="1:8">
-      <c r="A94" s="14">
+        <v>246</v>
+      </c>
+      <c r="F93" s="4"/>
+      <c r="G93" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="H93" s="4"/>
+    </row>
+    <row r="94" ht="34" spans="1:8">
+      <c r="A94" s="6">
         <v>84</v>
       </c>
       <c r="B94" s="7" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C94" s="7" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D94" s="7" t="s">
+        <v>248</v>
+      </c>
+      <c r="E94" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="F94" s="4"/>
+      <c r="G94" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="H94" s="4"/>
+    </row>
+    <row r="95" ht="34" spans="1:8">
+      <c r="A95" s="6">
+        <v>85</v>
+      </c>
+      <c r="B95" s="7" t="s">
         <v>247</v>
       </c>
-      <c r="E94" s="7" t="s">
-        <v>248</v>
-      </c>
-      <c r="F94" s="16"/>
-      <c r="G94" s="17"/>
-      <c r="H94" s="16"/>
-    </row>
-    <row r="95" spans="1:8">
-      <c r="A95" s="14">
-        <v>85</v>
-      </c>
-      <c r="B95" s="7" t="s">
-        <v>246</v>
-      </c>
       <c r="C95" s="7" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D95" s="7" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E95" s="7" t="s">
-        <v>250</v>
-      </c>
-      <c r="F95" s="16"/>
-      <c r="G95" s="17"/>
-      <c r="H95" s="16"/>
-    </row>
-    <row r="96" spans="1:8">
-      <c r="A96" s="14">
+        <v>251</v>
+      </c>
+      <c r="F95" s="4"/>
+      <c r="G95" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="H95" s="4"/>
+    </row>
+    <row r="96" ht="34" spans="1:8">
+      <c r="A96" s="6">
         <v>86</v>
       </c>
       <c r="B96" s="7" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C96" s="7" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D96" s="7" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E96" s="7" t="s">
-        <v>252</v>
-      </c>
-      <c r="F96" s="16"/>
-      <c r="G96" s="17"/>
-      <c r="H96" s="16"/>
-    </row>
-    <row r="97" spans="1:8">
-      <c r="A97" s="14">
+        <v>253</v>
+      </c>
+      <c r="F96" s="4"/>
+      <c r="G96" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="H96" s="4"/>
+    </row>
+    <row r="97" ht="34" spans="1:8">
+      <c r="A97" s="6">
         <v>87</v>
       </c>
       <c r="B97" s="7">
@@ -3650,37 +4430,41 @@
         <v>66</v>
       </c>
       <c r="D97" s="7" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E97" s="7" t="s">
-        <v>254</v>
-      </c>
-      <c r="F97" s="16"/>
-      <c r="G97" s="17"/>
-      <c r="H97" s="16"/>
-    </row>
-    <row r="98" spans="1:8">
-      <c r="A98" s="14">
+        <v>255</v>
+      </c>
+      <c r="F97" s="4"/>
+      <c r="G97" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="H97" s="4"/>
+    </row>
+    <row r="98" ht="34" spans="1:8">
+      <c r="A98" s="6">
         <v>88</v>
       </c>
       <c r="B98" s="7">
         <v>9.5</v>
       </c>
       <c r="C98" s="7" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D98" s="7" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E98" s="7" t="s">
-        <v>255</v>
-      </c>
-      <c r="F98" s="16"/>
-      <c r="G98" s="17"/>
-      <c r="H98" s="16"/>
-    </row>
-    <row r="99" spans="1:8">
-      <c r="A99" s="14">
+        <v>256</v>
+      </c>
+      <c r="F98" s="4"/>
+      <c r="G98" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="H98" s="4"/>
+    </row>
+    <row r="99" ht="34" spans="1:8">
+      <c r="A99" s="6">
         <v>89</v>
       </c>
       <c r="B99" s="7">
@@ -3690,89 +4474,97 @@
         <v>66</v>
       </c>
       <c r="D99" s="7" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E99" s="7" t="s">
-        <v>257</v>
-      </c>
-      <c r="F99" s="16"/>
-      <c r="G99" s="17"/>
-      <c r="H99" s="16"/>
-    </row>
-    <row r="100" spans="1:8">
-      <c r="A100" s="14">
+        <v>258</v>
+      </c>
+      <c r="F99" s="4"/>
+      <c r="G99" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="H99" s="4"/>
+    </row>
+    <row r="100" ht="51" spans="1:8">
+      <c r="A100" s="6">
         <v>90</v>
       </c>
       <c r="B100" s="7">
         <v>9.6</v>
       </c>
       <c r="C100" s="7" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D100" s="7" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E100" s="7" t="s">
-        <v>259</v>
-      </c>
-      <c r="F100" s="16"/>
-      <c r="G100" s="17"/>
-      <c r="H100" s="16"/>
-    </row>
-    <row r="101" spans="1:8">
-      <c r="A101" s="14">
+        <v>260</v>
+      </c>
+      <c r="F100" s="4"/>
+      <c r="G100" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="H100" s="4"/>
+    </row>
+    <row r="101" ht="34" spans="1:8">
+      <c r="A101" s="6">
         <v>91</v>
       </c>
       <c r="B101" s="7">
         <v>9.6</v>
       </c>
       <c r="C101" s="7" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D101" s="7" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E101" s="7" t="s">
-        <v>261</v>
-      </c>
-      <c r="F101" s="16"/>
-      <c r="G101" s="17"/>
-      <c r="H101" s="16"/>
-    </row>
-    <row r="102" spans="1:8">
-      <c r="A102" s="14">
+        <v>262</v>
+      </c>
+      <c r="F101" s="4"/>
+      <c r="G101" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="H101" s="4"/>
+    </row>
+    <row r="102" ht="51" spans="1:8">
+      <c r="A102" s="6">
         <v>92</v>
       </c>
       <c r="B102" s="7">
         <v>9.6</v>
       </c>
       <c r="C102" s="7" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D102" s="7" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E102" s="7" t="s">
-        <v>263</v>
-      </c>
-      <c r="F102" s="16"/>
-      <c r="G102" s="17"/>
-      <c r="H102" s="16"/>
-    </row>
-    <row r="103" spans="1:8" customHeight="1" ht="24">
-      <c r="A103" s="13" t="s">
         <v>264</v>
       </c>
-      <c r="B103" s="11"/>
-      <c r="C103" s="11"/>
-      <c r="D103" s="11"/>
-      <c r="E103" s="11"/>
-      <c r="F103" s="16"/>
-      <c r="G103" s="17"/>
-      <c r="H103" s="16"/>
-    </row>
-    <row r="104" spans="1:8">
-      <c r="A104" s="14">
+      <c r="F102" s="4"/>
+      <c r="G102" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="H102" s="4"/>
+    </row>
+    <row r="103" ht="24" customHeight="1" spans="1:8">
+      <c r="A103" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="B103" s="3"/>
+      <c r="C103" s="3"/>
+      <c r="D103" s="3"/>
+      <c r="E103" s="3"/>
+      <c r="F103" s="4"/>
+      <c r="G103" s="5"/>
+      <c r="H103" s="4"/>
+    </row>
+    <row r="104" ht="34" spans="1:8">
+      <c r="A104" s="6">
         <v>93</v>
       </c>
       <c r="B104" s="7">
@@ -3782,17 +4574,19 @@
         <v>66</v>
       </c>
       <c r="D104" s="7" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E104" s="7" t="s">
-        <v>266</v>
-      </c>
-      <c r="F104" s="16"/>
-      <c r="G104" s="17"/>
-      <c r="H104" s="16"/>
-    </row>
-    <row r="105" spans="1:8">
-      <c r="A105" s="14">
+        <v>267</v>
+      </c>
+      <c r="F104" s="4"/>
+      <c r="G104" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="H104" s="4"/>
+    </row>
+    <row r="105" ht="17" spans="1:8">
+      <c r="A105" s="6">
         <v>94</v>
       </c>
       <c r="B105" s="7">
@@ -3802,37 +4596,41 @@
         <v>66</v>
       </c>
       <c r="D105" s="7" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E105" s="7" t="s">
-        <v>268</v>
-      </c>
-      <c r="F105" s="16"/>
-      <c r="G105" s="17"/>
-      <c r="H105" s="16"/>
-    </row>
-    <row r="106" spans="1:8">
-      <c r="A106" s="14">
+        <v>269</v>
+      </c>
+      <c r="F105" s="4"/>
+      <c r="G105" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="H105" s="4"/>
+    </row>
+    <row r="106" ht="17" spans="1:8">
+      <c r="A106" s="6">
         <v>95</v>
       </c>
       <c r="B106" s="7">
         <v>10.2</v>
       </c>
       <c r="C106" s="7" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D106" s="7" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E106" s="7" t="s">
-        <v>270</v>
-      </c>
-      <c r="F106" s="16"/>
-      <c r="G106" s="17"/>
-      <c r="H106" s="16"/>
-    </row>
-    <row r="107" spans="1:8">
-      <c r="A107" s="14">
+        <v>271</v>
+      </c>
+      <c r="F106" s="4"/>
+      <c r="G106" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="H106" s="4"/>
+    </row>
+    <row r="107" ht="17" spans="1:8">
+      <c r="A107" s="6">
         <v>96</v>
       </c>
       <c r="B107" s="7">
@@ -3842,17 +4640,19 @@
         <v>66</v>
       </c>
       <c r="D107" s="7" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E107" s="7" t="s">
-        <v>272</v>
-      </c>
-      <c r="F107" s="16"/>
-      <c r="G107" s="17"/>
-      <c r="H107" s="16"/>
-    </row>
-    <row r="108" spans="1:8">
-      <c r="A108" s="14">
+        <v>273</v>
+      </c>
+      <c r="F107" s="4"/>
+      <c r="G107" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="H107" s="4"/>
+    </row>
+    <row r="108" ht="17" spans="1:8">
+      <c r="A108" s="6">
         <v>97</v>
       </c>
       <c r="B108" s="7">
@@ -3862,117 +4662,129 @@
         <v>66</v>
       </c>
       <c r="D108" s="7" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E108" s="7" t="s">
-        <v>274</v>
-      </c>
-      <c r="F108" s="16"/>
-      <c r="G108" s="17"/>
-      <c r="H108" s="16"/>
-    </row>
-    <row r="109" spans="1:8">
-      <c r="A109" s="15">
+        <v>275</v>
+      </c>
+      <c r="F108" s="4"/>
+      <c r="G108" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="H108" s="4"/>
+    </row>
+    <row r="109" ht="34" spans="1:8">
+      <c r="A109" s="8">
         <v>98</v>
       </c>
-      <c r="B109" s="12" t="s">
-        <v>275</v>
+      <c r="B109" s="9" t="s">
+        <v>276</v>
       </c>
       <c r="C109" s="10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D109" s="10" t="s">
+        <v>277</v>
+      </c>
+      <c r="E109" s="10" t="s">
+        <v>278</v>
+      </c>
+      <c r="F109" s="4"/>
+      <c r="G109" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="H109" s="4"/>
+    </row>
+    <row r="110" ht="17" spans="1:8">
+      <c r="A110" s="8">
+        <v>99</v>
+      </c>
+      <c r="B110" s="9" t="s">
         <v>276</v>
       </c>
-      <c r="E109" s="10" t="s">
-        <v>277</v>
-      </c>
-      <c r="F109" s="16"/>
-      <c r="G109" s="17"/>
-      <c r="H109" s="16"/>
-    </row>
-    <row r="110" spans="1:8">
-      <c r="A110" s="15">
-        <v>99</v>
-      </c>
-      <c r="B110" s="12" t="s">
-        <v>275</v>
-      </c>
       <c r="C110" s="10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D110" s="10" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="E110" s="10" t="s">
-        <v>279</v>
-      </c>
-      <c r="F110" s="16"/>
-      <c r="G110" s="17"/>
-      <c r="H110" s="16"/>
-    </row>
-    <row r="111" spans="1:8">
-      <c r="A111" s="14">
+        <v>280</v>
+      </c>
+      <c r="F110" s="4"/>
+      <c r="G110" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="H110" s="4"/>
+    </row>
+    <row r="111" ht="34" spans="1:8">
+      <c r="A111" s="6">
         <v>100</v>
       </c>
       <c r="B111" s="7">
         <v>10.3</v>
       </c>
       <c r="C111" s="7" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D111" s="7" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="E111" s="7" t="s">
-        <v>281</v>
-      </c>
-      <c r="F111" s="16"/>
-      <c r="G111" s="17"/>
-      <c r="H111" s="16"/>
-    </row>
-    <row r="112" spans="1:8">
-      <c r="A112" s="14">
+        <v>282</v>
+      </c>
+      <c r="F111" s="4"/>
+      <c r="G111" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="H111" s="4"/>
+    </row>
+    <row r="112" ht="34" spans="1:8">
+      <c r="A112" s="6">
         <v>101</v>
       </c>
       <c r="B112" s="7">
         <v>10.4</v>
       </c>
       <c r="C112" s="7" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D112" s="7" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E112" s="7" t="s">
-        <v>283</v>
-      </c>
-      <c r="F112" s="16"/>
-      <c r="G112" s="17"/>
-      <c r="H112" s="16"/>
-    </row>
-    <row r="113" spans="1:8">
-      <c r="A113" s="14">
+        <v>284</v>
+      </c>
+      <c r="F112" s="4"/>
+      <c r="G112" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="H112" s="4"/>
+    </row>
+    <row r="113" ht="17" spans="1:8">
+      <c r="A113" s="6">
         <v>102</v>
       </c>
       <c r="B113" s="7">
         <v>10.4</v>
       </c>
       <c r="C113" s="7" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D113" s="7" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E113" s="7" t="s">
-        <v>284</v>
-      </c>
-      <c r="F113" s="16"/>
-      <c r="G113" s="17"/>
-      <c r="H113" s="16"/>
-    </row>
-    <row r="114" spans="1:8">
-      <c r="A114" s="14">
+        <v>285</v>
+      </c>
+      <c r="F113" s="4"/>
+      <c r="G113" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="H113" s="4"/>
+    </row>
+    <row r="114" ht="17" spans="1:8">
+      <c r="A114" s="6">
         <v>103</v>
       </c>
       <c r="B114" s="7">
@@ -3982,118 +4794,132 @@
         <v>66</v>
       </c>
       <c r="D114" s="7" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="E114" s="7">
-        <v>403.0</v>
-      </c>
-      <c r="F114" s="16"/>
-      <c r="G114" s="17"/>
-      <c r="H114" s="16"/>
-    </row>
-    <row r="115" spans="1:8">
-      <c r="A115" s="14">
+        <v>403</v>
+      </c>
+      <c r="F114" s="4"/>
+      <c r="G114" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="H114" s="4"/>
+    </row>
+    <row r="115" ht="34" spans="1:8">
+      <c r="A115" s="6">
         <v>104</v>
       </c>
       <c r="B115" s="7">
         <v>10.5</v>
       </c>
       <c r="C115" s="7" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D115" s="7" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="E115" s="7" t="s">
-        <v>287</v>
-      </c>
-      <c r="F115" s="16"/>
-      <c r="G115" s="17"/>
-      <c r="H115" s="16"/>
-    </row>
-    <row r="116" spans="1:8">
-      <c r="A116" s="14">
+        <v>288</v>
+      </c>
+      <c r="F115" s="4"/>
+      <c r="G115" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="H115" s="4"/>
+    </row>
+    <row r="116" ht="17" spans="1:8">
+      <c r="A116" s="6">
         <v>105</v>
       </c>
       <c r="B116" s="7">
         <v>10.5</v>
       </c>
       <c r="C116" s="7" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D116" s="7" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E116" s="7" t="s">
-        <v>289</v>
-      </c>
-      <c r="F116" s="16"/>
-      <c r="G116" s="17"/>
-      <c r="H116" s="16"/>
-    </row>
-    <row r="117" spans="1:8">
-      <c r="A117" s="14">
+        <v>290</v>
+      </c>
+      <c r="F116" s="4"/>
+      <c r="G116" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="H116" s="4"/>
+    </row>
+    <row r="117" ht="34" spans="1:8">
+      <c r="A117" s="6">
         <v>106</v>
       </c>
       <c r="B117" s="7">
         <v>10.6</v>
       </c>
       <c r="C117" s="7" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D117" s="7" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E117" s="7" t="s">
-        <v>291</v>
-      </c>
-      <c r="F117" s="16"/>
-      <c r="G117" s="17"/>
-      <c r="H117" s="16"/>
-    </row>
-    <row r="118" spans="1:8">
-      <c r="A118" s="14">
+        <v>292</v>
+      </c>
+      <c r="F117" s="4"/>
+      <c r="G117" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="H117" s="4"/>
+    </row>
+    <row r="118" ht="17" spans="1:8">
+      <c r="A118" s="6">
         <v>107</v>
       </c>
       <c r="B118" s="7">
         <v>10.6</v>
       </c>
       <c r="C118" s="7" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D118" s="7" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E118" s="7" t="s">
-        <v>293</v>
-      </c>
-      <c r="F118" s="16"/>
-      <c r="G118" s="17"/>
-      <c r="H118" s="16"/>
-    </row>
-    <row r="119" spans="1:8">
-      <c r="A119" s="14">
+        <v>294</v>
+      </c>
+      <c r="F118" s="4"/>
+      <c r="G118" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="H118" s="4"/>
+    </row>
+    <row r="119" ht="34" spans="1:8">
+      <c r="A119" s="6">
         <v>108</v>
       </c>
       <c r="B119" s="7">
         <v>10.6</v>
       </c>
       <c r="C119" s="7" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D119" s="7" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="E119" s="7" t="s">
-        <v>295</v>
-      </c>
-      <c r="F119" s="16"/>
-      <c r="G119" s="17"/>
-      <c r="H119" s="16"/>
+        <v>296</v>
+      </c>
+      <c r="F119" s="4"/>
+      <c r="G119" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="H119" s="4"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H119"/>
-  <mergeCells>
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:H119" etc:filterBottomFollowUsedRange="0">
+    <extLst/>
+  </autoFilter>
+  <mergeCells count="10">
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A11:H11"/>
     <mergeCell ref="A21:H21"/>
@@ -4105,49 +4931,13 @@
     <mergeCell ref="A73:H73"/>
     <mergeCell ref="A103:H103"/>
   </mergeCells>
-  <dataValidations count="10">
-    <dataValidation type="list" errorStyle="information" operator="between" allowBlank="1" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="G3:G10">
-      <formula1>"OK,GAGAL,TERLEWAT,N/A"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="between" allowBlank="1" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="G12:G20">
-      <formula1>"OK,GAGAL,TERLEWAT,N/A"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="between" allowBlank="1" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="G22:G27">
-      <formula1>"OK,GAGAL,TERLEWAT,N/A"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="between" allowBlank="1" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="G29:G34">
-      <formula1>"OK,GAGAL,TERLEWAT,N/A"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="between" allowBlank="1" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="G36:G46">
-      <formula1>"OK,GAGAL,TERLEWAT,N/A"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="between" allowBlank="1" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="G48:G55">
-      <formula1>"OK,GAGAL,TERLEWAT,N/A"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="between" allowBlank="1" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="G57:G66">
-      <formula1>"OK,GAGAL,TERLEWAT,N/A"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="between" allowBlank="1" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="G68:G72">
-      <formula1>"OK,GAGAL,TERLEWAT,N/A"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="between" allowBlank="1" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="G74:G102">
-      <formula1>"OK,GAGAL,TERLEWAT,N/A"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="between" allowBlank="1" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="G104:G119">
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" sqref="G109 G3:G10 G12:G20 G22:G27 G29:G34 G36:G46 G48:G55 G57:G66 G68:G72 G74:G96 G97:G102 G104:G108 G110:G119" errorStyle="information">
       <formula1>"OK,GAGAL,TERLEWAT,N/A"</formula1>
     </dataValidation>
   </dataValidations>
-  <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
-  <headerFooter differentOddEven="false" differentFirst="false" scaleWithDoc="true" alignWithMargins="true">
-    <oddHeader/>
-    <oddFooter/>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
-  <tableParts count="0"/>
+  <pageSetup paperSize="1" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>